--- a/docs/reports/ER_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/ER_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -857,19 +875,19 @@
         <f>'Daily Breakdown'!J276</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -877,24 +895,24 @@
         <f>'Daily Breakdown'!K276</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
       <c r="S5" s="8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T5" s="12">
         <f>ROUND(F5*(1-M5)*(1-Q5),2)</f>
@@ -939,7 +957,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1011,7 +1028,7 @@
       <c r="C4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>243.75</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1051,7 +1068,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>244.03</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1091,7 +1108,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>243.62</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1131,7 +1148,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>243.92</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1171,7 +1188,7 @@
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>243.69</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1211,7 +1228,7 @@
       <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>199.73</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1251,7 +1268,7 @@
       <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>232.23</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1291,7 +1308,7 @@
       <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>199.72</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1331,7 +1348,7 @@
       <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1371,7 +1388,7 @@
       <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>232.24</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1411,7 +1428,7 @@
       <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>231.65</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1451,7 +1468,7 @@
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>232.24</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1491,7 +1508,7 @@
       <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>204.46</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1531,7 +1548,7 @@
       <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>199.49</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1571,7 +1588,7 @@
       <c r="C18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>199.54</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1611,7 +1628,7 @@
       <c r="C19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>232.24</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1651,7 +1668,7 @@
       <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1691,7 +1708,7 @@
       <c r="C21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>93.98999999999999</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1731,7 +1748,7 @@
       <c r="C22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1771,7 +1788,7 @@
       <c r="C23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>93.70999999999999</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1811,7 +1828,7 @@
       <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>82.5</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1851,7 +1868,7 @@
       <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>82.52</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1891,7 +1908,7 @@
       <c r="C26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>150.34</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1931,7 +1948,7 @@
       <c r="C27" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1971,7 +1988,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>94.12</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2011,7 +2028,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>82.62</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2051,7 +2068,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>8.59</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2091,7 +2108,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>82.52</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2131,7 +2148,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>81.67</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2171,7 +2188,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>39.27</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2211,7 +2228,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>59.82</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2251,7 +2268,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>82.64</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2291,7 +2308,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="49" t="n">
         <v>0.25</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2331,7 +2348,7 @@
       <c r="C37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="49" t="n">
         <v>39.82</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2371,7 +2388,7 @@
       <c r="C38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="49" t="n">
         <v>0.23</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2411,7 +2428,7 @@
       <c r="C39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="49" t="n">
         <v>0.51</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2451,7 +2468,7 @@
       <c r="C40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="49" t="n">
         <v>4.47</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2492,7 +2509,7 @@
         <f>SUM(C4:C40)</f>
         <v/>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="50">
         <f>SUM(D4:D40)</f>
         <v/>
       </c>
@@ -2539,7 +2556,7 @@
       <c r="C42" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="49" t="n">
         <v>244.01</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2579,7 +2596,7 @@
       <c r="C43" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="49" t="n">
         <v>244.03</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2619,7 +2636,7 @@
       <c r="C44" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="49" t="n">
         <v>243.63</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2659,7 +2676,7 @@
       <c r="C45" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="49" t="n">
         <v>243.67</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2699,7 +2716,7 @@
       <c r="C46" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="49" t="n">
         <v>243.91</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2739,7 +2756,7 @@
       <c r="C47" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="49" t="n">
         <v>232.24</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2779,7 +2796,7 @@
       <c r="C48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="49" t="n">
         <v>231.67</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2819,7 +2836,7 @@
       <c r="C49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="49" t="n">
         <v>205.13</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2859,7 +2876,7 @@
       <c r="C50" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="49" t="n">
         <v>232.26</v>
       </c>
       <c r="E50" s="18" t="n">
@@ -2899,7 +2916,7 @@
       <c r="C51" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="49" t="n">
         <v>198.7</v>
       </c>
       <c r="E51" s="18" t="n">
@@ -2939,7 +2956,7 @@
       <c r="C52" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="49" t="n">
         <v>94.25</v>
       </c>
       <c r="E52" s="18" t="n">
@@ -2979,7 +2996,7 @@
       <c r="C53" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="49" t="n">
         <v>216.58</v>
       </c>
       <c r="E53" s="18" t="n">
@@ -3019,7 +3036,7 @@
       <c r="C54" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="49" t="n">
         <v>172.41</v>
       </c>
       <c r="E54" s="18" t="n">
@@ -3059,7 +3076,7 @@
       <c r="C55" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="49" t="n">
         <v>199.46</v>
       </c>
       <c r="E55" s="18" t="n">
@@ -3099,7 +3116,7 @@
       <c r="C56" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E56" s="18" t="n">
@@ -3139,7 +3156,7 @@
       <c r="C57" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="49" t="n">
         <v>231.66</v>
       </c>
       <c r="E57" s="18" t="n">
@@ -3179,7 +3196,7 @@
       <c r="C58" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="49" t="n">
         <v>199.53</v>
       </c>
       <c r="E58" s="18" t="n">
@@ -3219,7 +3236,7 @@
       <c r="C59" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="49" t="n">
         <v>203.78</v>
       </c>
       <c r="E59" s="18" t="n">
@@ -3259,7 +3276,7 @@
       <c r="C60" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E60" s="18" t="n">
@@ -3299,7 +3316,7 @@
       <c r="C61" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E61" s="18" t="n">
@@ -3339,7 +3356,7 @@
       <c r="C62" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="49" t="n">
         <v>198.45</v>
       </c>
       <c r="E62" s="18" t="n">
@@ -3379,7 +3396,7 @@
       <c r="C63" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="49" t="n">
         <v>94.01000000000001</v>
       </c>
       <c r="E63" s="18" t="n">
@@ -3419,7 +3436,7 @@
       <c r="C64" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E64" s="18" t="n">
@@ -3459,7 +3476,7 @@
       <c r="C65" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="49" t="n">
         <v>82.48999999999999</v>
       </c>
       <c r="E65" s="18" t="n">
@@ -3499,7 +3516,7 @@
       <c r="C66" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="49" t="n">
         <v>79.62</v>
       </c>
       <c r="E66" s="18" t="n">
@@ -3539,7 +3556,7 @@
       <c r="C67" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E67" s="18" t="n">
@@ -3579,7 +3596,7 @@
       <c r="C68" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="49" t="n">
         <v>94.2</v>
       </c>
       <c r="E68" s="18" t="n">
@@ -3619,7 +3636,7 @@
       <c r="C69" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="49" t="n">
         <v>82.53</v>
       </c>
       <c r="E69" s="18" t="n">
@@ -3659,7 +3676,7 @@
       <c r="C70" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="49" t="n">
         <v>81.29000000000001</v>
       </c>
       <c r="E70" s="18" t="n">
@@ -3699,7 +3716,7 @@
       <c r="C71" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="49" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="E71" s="18" t="n">
@@ -3739,7 +3756,7 @@
       <c r="C72" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="49" t="n">
         <v>84.48999999999999</v>
       </c>
       <c r="E72" s="18" t="n">
@@ -3779,7 +3796,7 @@
       <c r="C73" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="49" t="n">
         <v>82.51000000000001</v>
       </c>
       <c r="E73" s="18" t="n">
@@ -3819,7 +3836,7 @@
       <c r="C74" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="49" t="n">
         <v>60.77</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -3859,7 +3876,7 @@
       <c r="C75" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="49" t="n">
         <v>9.970000000000001</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -3899,7 +3916,7 @@
       <c r="C76" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="49" t="n">
         <v>0.23</v>
       </c>
       <c r="E76" s="18" t="n">
@@ -3939,7 +3956,7 @@
       <c r="C77" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -3979,7 +3996,7 @@
       <c r="C78" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="49" t="n">
         <v>0.42</v>
       </c>
       <c r="E78" s="18" t="n">
@@ -4019,7 +4036,7 @@
       <c r="C79" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="49" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -4059,7 +4076,7 @@
       <c r="C80" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="49" t="n">
         <v>4.24</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -4100,7 +4117,7 @@
         <f>SUM(C42:C80)</f>
         <v/>
       </c>
-      <c r="D81" s="22">
+      <c r="D81" s="50">
         <f>SUM(D42:D80)</f>
         <v/>
       </c>
@@ -4147,7 +4164,7 @@
       <c r="C82" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="49" t="n">
         <v>244.02</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -4187,7 +4204,7 @@
       <c r="C83" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="49" t="n">
         <v>244.01</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -4227,7 +4244,7 @@
       <c r="C84" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D84" s="17" t="n">
+      <c r="D84" s="49" t="n">
         <v>243.63</v>
       </c>
       <c r="E84" s="18" t="n">
@@ -4267,7 +4284,7 @@
       <c r="C85" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="49" t="n">
         <v>243.89</v>
       </c>
       <c r="E85" s="18" t="n">
@@ -4307,7 +4324,7 @@
       <c r="C86" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="17" t="n">
+      <c r="D86" s="49" t="n">
         <v>199.74</v>
       </c>
       <c r="E86" s="18" t="n">
@@ -4347,7 +4364,7 @@
       <c r="C87" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="49" t="n">
         <v>231.66</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -4387,7 +4404,7 @@
       <c r="C88" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="49" t="n">
         <v>232.23</v>
       </c>
       <c r="E88" s="18" t="n">
@@ -4427,7 +4444,7 @@
       <c r="C89" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="49" t="n">
         <v>231.66</v>
       </c>
       <c r="E89" s="18" t="n">
@@ -4467,7 +4484,7 @@
       <c r="C90" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="49" t="n">
         <v>233.48</v>
       </c>
       <c r="E90" s="18" t="n">
@@ -4507,7 +4524,7 @@
       <c r="C91" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D91" s="49" t="n">
         <v>110.03</v>
       </c>
       <c r="E91" s="18" t="n">
@@ -4547,7 +4564,7 @@
       <c r="C92" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E92" s="18" t="n">
@@ -4587,7 +4604,7 @@
       <c r="C93" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="49" t="n">
         <v>199.04</v>
       </c>
       <c r="E93" s="18" t="n">
@@ -4627,7 +4644,7 @@
       <c r="C94" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="49" t="n">
         <v>231.62</v>
       </c>
       <c r="E94" s="18" t="n">
@@ -4667,7 +4684,7 @@
       <c r="C95" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="49" t="n">
         <v>199.02</v>
       </c>
       <c r="E95" s="18" t="n">
@@ -4707,7 +4724,7 @@
       <c r="C96" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E96" s="18" t="n">
@@ -4747,7 +4764,7 @@
       <c r="C97" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="49" t="n">
         <v>199.35</v>
       </c>
       <c r="E97" s="18" t="n">
@@ -4787,7 +4804,7 @@
       <c r="C98" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="49" t="n">
         <v>205.7</v>
       </c>
       <c r="E98" s="18" t="n">
@@ -4827,7 +4844,7 @@
       <c r="C99" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="49" t="n">
         <v>94.28</v>
       </c>
       <c r="E99" s="18" t="n">
@@ -4867,7 +4884,7 @@
       <c r="C100" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="49" t="n">
         <v>199.53</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -4907,7 +4924,7 @@
       <c r="C101" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="49" t="n">
         <v>199.39</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -4947,7 +4964,7 @@
       <c r="C102" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -4987,7 +5004,7 @@
       <c r="C103" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="49" t="n">
         <v>171.45</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -5027,7 +5044,7 @@
       <c r="C104" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="49" t="n">
         <v>198.49</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -5067,7 +5084,7 @@
       <c r="C105" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="49" t="n">
         <v>198.92</v>
       </c>
       <c r="E105" s="18" t="n">
@@ -5107,7 +5124,7 @@
       <c r="C106" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="49" t="n">
         <v>187.97</v>
       </c>
       <c r="E106" s="18" t="n">
@@ -5147,7 +5164,7 @@
       <c r="C107" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="49" t="n">
         <v>82.63</v>
       </c>
       <c r="E107" s="18" t="n">
@@ -5187,7 +5204,7 @@
       <c r="C108" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="49" t="n">
         <v>199.39</v>
       </c>
       <c r="E108" s="18" t="n">
@@ -5227,7 +5244,7 @@
       <c r="C109" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="49" t="n">
         <v>152.22</v>
       </c>
       <c r="E109" s="18" t="n">
@@ -5267,7 +5284,7 @@
       <c r="C110" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E110" s="18" t="n">
@@ -5307,7 +5324,7 @@
       <c r="C111" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="49" t="n">
         <v>81.41</v>
       </c>
       <c r="E111" s="18" t="n">
@@ -5347,7 +5364,7 @@
       <c r="C112" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="49" t="n">
         <v>93.98999999999999</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -5387,7 +5404,7 @@
       <c r="C113" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="49" t="n">
         <v>94.14</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -5427,7 +5444,7 @@
       <c r="C114" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="17" t="n">
+      <c r="D114" s="49" t="n">
         <v>232.19</v>
       </c>
       <c r="E114" s="18" t="n">
@@ -5467,7 +5484,7 @@
       <c r="C115" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="49" t="n">
         <v>82</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -5507,7 +5524,7 @@
       <c r="C116" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="49" t="n">
         <v>82.58</v>
       </c>
       <c r="E116" s="18" t="n">
@@ -5547,7 +5564,7 @@
       <c r="C117" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="49" t="n">
         <v>94.18000000000001</v>
       </c>
       <c r="E117" s="18" t="n">
@@ -5587,7 +5604,7 @@
       <c r="C118" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="17" t="n">
+      <c r="D118" s="49" t="n">
         <v>90.89</v>
       </c>
       <c r="E118" s="18" t="n">
@@ -5627,7 +5644,7 @@
       <c r="C119" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="49" t="n">
         <v>82.5</v>
       </c>
       <c r="E119" s="18" t="n">
@@ -5667,7 +5684,7 @@
       <c r="C120" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="49" t="n">
         <v>4.87</v>
       </c>
       <c r="E120" s="18" t="n">
@@ -5707,7 +5724,7 @@
       <c r="C121" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="49" t="n">
         <v>0.24</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -5747,7 +5764,7 @@
       <c r="C122" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="17" t="n">
+      <c r="D122" s="49" t="n">
         <v>7.41</v>
       </c>
       <c r="E122" s="18" t="n">
@@ -5788,7 +5805,7 @@
         <f>SUM(C82:C122)</f>
         <v/>
       </c>
-      <c r="D123" s="22">
+      <c r="D123" s="50">
         <f>SUM(D82:D122)</f>
         <v/>
       </c>
@@ -5835,7 +5852,7 @@
       <c r="C124" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D124" s="17" t="n">
+      <c r="D124" s="49" t="n">
         <v>243.75</v>
       </c>
       <c r="E124" s="18" t="n">
@@ -5875,7 +5892,7 @@
       <c r="C125" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D125" s="17" t="n">
+      <c r="D125" s="49" t="n">
         <v>243.62</v>
       </c>
       <c r="E125" s="18" t="n">
@@ -5915,7 +5932,7 @@
       <c r="C126" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D126" s="17" t="n">
+      <c r="D126" s="49" t="n">
         <v>243.67</v>
       </c>
       <c r="E126" s="18" t="n">
@@ -5955,7 +5972,7 @@
       <c r="C127" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D127" s="17" t="n">
+      <c r="D127" s="49" t="n">
         <v>244.03</v>
       </c>
       <c r="E127" s="18" t="n">
@@ -5995,7 +6012,7 @@
       <c r="C128" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="49" t="n">
         <v>243.91</v>
       </c>
       <c r="E128" s="18" t="n">
@@ -6035,7 +6052,7 @@
       <c r="C129" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D129" s="17" t="n">
+      <c r="D129" s="49" t="n">
         <v>199.53</v>
       </c>
       <c r="E129" s="18" t="n">
@@ -6075,7 +6092,7 @@
       <c r="C130" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D130" s="17" t="n">
+      <c r="D130" s="49" t="n">
         <v>232.21</v>
       </c>
       <c r="E130" s="18" t="n">
@@ -6115,7 +6132,7 @@
       <c r="C131" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="17" t="n">
+      <c r="D131" s="49" t="n">
         <v>199.39</v>
       </c>
       <c r="E131" s="18" t="n">
@@ -6155,7 +6172,7 @@
       <c r="C132" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D132" s="17" t="n">
+      <c r="D132" s="49" t="n">
         <v>232.23</v>
       </c>
       <c r="E132" s="18" t="n">
@@ -6195,7 +6212,7 @@
       <c r="C133" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="17" t="n">
+      <c r="D133" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E133" s="18" t="n">
@@ -6235,7 +6252,7 @@
       <c r="C134" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="17" t="n">
+      <c r="D134" s="49" t="n">
         <v>199.2</v>
       </c>
       <c r="E134" s="18" t="n">
@@ -6275,7 +6292,7 @@
       <c r="C135" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D135" s="17" t="n">
+      <c r="D135" s="49" t="n">
         <v>199.38</v>
       </c>
       <c r="E135" s="18" t="n">
@@ -6315,7 +6332,7 @@
       <c r="C136" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D136" s="17" t="n">
+      <c r="D136" s="49" t="n">
         <v>199.19</v>
       </c>
       <c r="E136" s="18" t="n">
@@ -6355,7 +6372,7 @@
       <c r="C137" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D137" s="17" t="n">
+      <c r="D137" s="49" t="n">
         <v>94.26000000000001</v>
       </c>
       <c r="E137" s="18" t="n">
@@ -6395,7 +6412,7 @@
       <c r="C138" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D138" s="17" t="n">
+      <c r="D138" s="49" t="n">
         <v>199.47</v>
       </c>
       <c r="E138" s="18" t="n">
@@ -6435,7 +6452,7 @@
       <c r="C139" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D139" s="17" t="n">
+      <c r="D139" s="49" t="n">
         <v>186.69</v>
       </c>
       <c r="E139" s="18" t="n">
@@ -6475,7 +6492,7 @@
       <c r="C140" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D140" s="17" t="n">
+      <c r="D140" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E140" s="18" t="n">
@@ -6515,7 +6532,7 @@
       <c r="C141" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D141" s="17" t="n">
+      <c r="D141" s="49" t="n">
         <v>199.45</v>
       </c>
       <c r="E141" s="18" t="n">
@@ -6555,7 +6572,7 @@
       <c r="C142" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D142" s="17" t="n">
+      <c r="D142" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E142" s="18" t="n">
@@ -6595,7 +6612,7 @@
       <c r="C143" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D143" s="17" t="n">
+      <c r="D143" s="49" t="n">
         <v>204.9</v>
       </c>
       <c r="E143" s="18" t="n">
@@ -6635,7 +6652,7 @@
       <c r="C144" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D144" s="17" t="n">
+      <c r="D144" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E144" s="18" t="n">
@@ -6675,7 +6692,7 @@
       <c r="C145" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D145" s="17" t="n">
+      <c r="D145" s="49" t="n">
         <v>232.16</v>
       </c>
       <c r="E145" s="18" t="n">
@@ -6715,7 +6732,7 @@
       <c r="C146" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D146" s="17" t="n">
+      <c r="D146" s="49" t="n">
         <v>163.55</v>
       </c>
       <c r="E146" s="18" t="n">
@@ -6755,7 +6772,7 @@
       <c r="C147" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D147" s="17" t="n">
+      <c r="D147" s="49" t="n">
         <v>187.97</v>
       </c>
       <c r="E147" s="18" t="n">
@@ -6795,7 +6812,7 @@
       <c r="C148" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D148" s="17" t="n">
+      <c r="D148" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E148" s="18" t="n">
@@ -6835,7 +6852,7 @@
       <c r="C149" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D149" s="17" t="n">
+      <c r="D149" s="49" t="n">
         <v>94.19</v>
       </c>
       <c r="E149" s="18" t="n">
@@ -6875,7 +6892,7 @@
       <c r="C150" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D150" s="17" t="n">
+      <c r="D150" s="49" t="n">
         <v>152.48</v>
       </c>
       <c r="E150" s="18" t="n">
@@ -6915,7 +6932,7 @@
       <c r="C151" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D151" s="17" t="n">
+      <c r="D151" s="49" t="n">
         <v>82.61</v>
       </c>
       <c r="E151" s="18" t="n">
@@ -6955,7 +6972,7 @@
       <c r="C152" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D152" s="17" t="n">
+      <c r="D152" s="49" t="n">
         <v>81.41</v>
       </c>
       <c r="E152" s="18" t="n">
@@ -6995,7 +7012,7 @@
       <c r="C153" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D153" s="17" t="n">
+      <c r="D153" s="49" t="n">
         <v>86.26000000000001</v>
       </c>
       <c r="E153" s="18" t="n">
@@ -7035,7 +7052,7 @@
       <c r="C154" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D154" s="17" t="n">
+      <c r="D154" s="49" t="n">
         <v>94.02</v>
       </c>
       <c r="E154" s="18" t="n">
@@ -7075,7 +7092,7 @@
       <c r="C155" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D155" s="17" t="n">
+      <c r="D155" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E155" s="18" t="n">
@@ -7115,7 +7132,7 @@
       <c r="C156" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D156" s="17" t="n">
+      <c r="D156" s="49" t="n">
         <v>81.36</v>
       </c>
       <c r="E156" s="18" t="n">
@@ -7155,7 +7172,7 @@
       <c r="C157" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D157" s="17" t="n">
+      <c r="D157" s="49" t="n">
         <v>82.52</v>
       </c>
       <c r="E157" s="18" t="n">
@@ -7195,7 +7212,7 @@
       <c r="C158" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D158" s="17" t="n">
+      <c r="D158" s="49" t="n">
         <v>72.41</v>
       </c>
       <c r="E158" s="18" t="n">
@@ -7235,7 +7252,7 @@
       <c r="C159" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D159" s="17" t="n">
+      <c r="D159" s="49" t="n">
         <v>232.18</v>
       </c>
       <c r="E159" s="18" t="n">
@@ -7275,7 +7292,7 @@
       <c r="C160" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D160" s="17" t="n">
+      <c r="D160" s="49" t="n">
         <v>82.62</v>
       </c>
       <c r="E160" s="18" t="n">
@@ -7315,7 +7332,7 @@
       <c r="C161" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D161" s="17" t="n">
+      <c r="D161" s="49" t="n">
         <v>0.51</v>
       </c>
       <c r="E161" s="18" t="n">
@@ -7355,7 +7372,7 @@
       <c r="C162" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D162" s="17" t="n">
+      <c r="D162" s="49" t="n">
         <v>0.49</v>
       </c>
       <c r="E162" s="18" t="n">
@@ -7395,7 +7412,7 @@
       <c r="C163" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="49" t="n">
         <v>0.05</v>
       </c>
       <c r="E163" s="18" t="n">
@@ -7435,7 +7452,7 @@
       <c r="C164" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="49" t="n">
         <v>0.04</v>
       </c>
       <c r="E164" s="18" t="n">
@@ -7476,7 +7493,7 @@
         <f>SUM(C124:C164)</f>
         <v/>
       </c>
-      <c r="D165" s="22">
+      <c r="D165" s="50">
         <f>SUM(D124:D164)</f>
         <v/>
       </c>
@@ -7523,7 +7540,7 @@
       <c r="C166" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D166" s="17" t="n">
+      <c r="D166" s="49" t="n">
         <v>244.01</v>
       </c>
       <c r="E166" s="18" t="n">
@@ -7563,7 +7580,7 @@
       <c r="C167" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D167" s="17" t="n">
+      <c r="D167" s="49" t="n">
         <v>244.03</v>
       </c>
       <c r="E167" s="18" t="n">
@@ -7603,7 +7620,7 @@
       <c r="C168" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D168" s="17" t="n">
+      <c r="D168" s="49" t="n">
         <v>243.73</v>
       </c>
       <c r="E168" s="18" t="n">
@@ -7643,7 +7660,7 @@
       <c r="C169" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="49" t="n">
         <v>243.66</v>
       </c>
       <c r="E169" s="18" t="n">
@@ -7683,7 +7700,7 @@
       <c r="C170" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D170" s="17" t="n">
+      <c r="D170" s="49" t="n">
         <v>243.91</v>
       </c>
       <c r="E170" s="18" t="n">
@@ -7723,7 +7740,7 @@
       <c r="C171" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D171" s="17" t="n">
+      <c r="D171" s="49" t="n">
         <v>198.84</v>
       </c>
       <c r="E171" s="18" t="n">
@@ -7763,7 +7780,7 @@
       <c r="C172" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D172" s="17" t="n">
+      <c r="D172" s="49" t="n">
         <v>231.65</v>
       </c>
       <c r="E172" s="18" t="n">
@@ -7803,7 +7820,7 @@
       <c r="C173" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D173" s="17" t="n">
+      <c r="D173" s="49" t="n">
         <v>94.27</v>
       </c>
       <c r="E173" s="18" t="n">
@@ -7843,7 +7860,7 @@
       <c r="C174" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D174" s="17" t="n">
+      <c r="D174" s="49" t="n">
         <v>232.24</v>
       </c>
       <c r="E174" s="18" t="n">
@@ -7883,7 +7900,7 @@
       <c r="C175" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D175" s="17" t="n">
+      <c r="D175" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E175" s="18" t="n">
@@ -7923,7 +7940,7 @@
       <c r="C176" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D176" s="17" t="n">
+      <c r="D176" s="49" t="n">
         <v>199.04</v>
       </c>
       <c r="E176" s="18" t="n">
@@ -7963,7 +7980,7 @@
       <c r="C177" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D177" s="17" t="n">
+      <c r="D177" s="49" t="n">
         <v>150.16</v>
       </c>
       <c r="E177" s="18" t="n">
@@ -8003,7 +8020,7 @@
       <c r="C178" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D178" s="17" t="n">
+      <c r="D178" s="49" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="E178" s="18" t="n">
@@ -8043,7 +8060,7 @@
       <c r="C179" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D179" s="17" t="n">
+      <c r="D179" s="49" t="n">
         <v>166.85</v>
       </c>
       <c r="E179" s="18" t="n">
@@ -8083,7 +8100,7 @@
       <c r="C180" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D180" s="17" t="n">
+      <c r="D180" s="49" t="n">
         <v>188.33</v>
       </c>
       <c r="E180" s="18" t="n">
@@ -8123,7 +8140,7 @@
       <c r="C181" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D181" s="17" t="n">
+      <c r="D181" s="49" t="n">
         <v>233.92</v>
       </c>
       <c r="E181" s="18" t="n">
@@ -8163,7 +8180,7 @@
       <c r="C182" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D182" s="17" t="n">
+      <c r="D182" s="49" t="n">
         <v>154.83</v>
       </c>
       <c r="E182" s="18" t="n">
@@ -8203,7 +8220,7 @@
       <c r="C183" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D183" s="17" t="n">
+      <c r="D183" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E183" s="18" t="n">
@@ -8243,7 +8260,7 @@
       <c r="C184" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D184" s="17" t="n">
+      <c r="D184" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E184" s="18" t="n">
@@ -8283,7 +8300,7 @@
       <c r="C185" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D185" s="17" t="n">
+      <c r="D185" s="49" t="n">
         <v>82.62</v>
       </c>
       <c r="E185" s="18" t="n">
@@ -8323,7 +8340,7 @@
       <c r="C186" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="17" t="n">
+      <c r="D186" s="49" t="n">
         <v>94.20999999999999</v>
       </c>
       <c r="E186" s="18" t="n">
@@ -8363,7 +8380,7 @@
       <c r="C187" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D187" s="17" t="n">
+      <c r="D187" s="49" t="n">
         <v>94.12</v>
       </c>
       <c r="E187" s="18" t="n">
@@ -8403,7 +8420,7 @@
       <c r="C188" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D188" s="17" t="n">
+      <c r="D188" s="49" t="n">
         <v>81.95</v>
       </c>
       <c r="E188" s="18" t="n">
@@ -8443,7 +8460,7 @@
       <c r="C189" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D189" s="17" t="n">
+      <c r="D189" s="49" t="n">
         <v>82.64</v>
       </c>
       <c r="E189" s="18" t="n">
@@ -8483,7 +8500,7 @@
       <c r="C190" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="17" t="n">
+      <c r="D190" s="49" t="n">
         <v>77.72</v>
       </c>
       <c r="E190" s="18" t="n">
@@ -8523,7 +8540,7 @@
       <c r="C191" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D191" s="17" t="n">
+      <c r="D191" s="49" t="n">
         <v>38.68</v>
       </c>
       <c r="E191" s="18" t="n">
@@ -8563,7 +8580,7 @@
       <c r="C192" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D192" s="17" t="n">
+      <c r="D192" s="49" t="n">
         <v>94.19</v>
       </c>
       <c r="E192" s="18" t="n">
@@ -8603,7 +8620,7 @@
       <c r="C193" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D193" s="17" t="n">
+      <c r="D193" s="49" t="n">
         <v>62.88</v>
       </c>
       <c r="E193" s="18" t="n">
@@ -8643,7 +8660,7 @@
       <c r="C194" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D194" s="17" t="n">
+      <c r="D194" s="49" t="n">
         <v>41.94</v>
       </c>
       <c r="E194" s="18" t="n">
@@ -8683,7 +8700,7 @@
       <c r="C195" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D195" s="17" t="n">
+      <c r="D195" s="49" t="n">
         <v>0.2</v>
       </c>
       <c r="E195" s="18" t="n">
@@ -8723,7 +8740,7 @@
       <c r="C196" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D196" s="17" t="n">
+      <c r="D196" s="49" t="n">
         <v>51.54</v>
       </c>
       <c r="E196" s="18" t="n">
@@ -8763,7 +8780,7 @@
       <c r="C197" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D197" s="17" t="n">
+      <c r="D197" s="49" t="n">
         <v>3.23</v>
       </c>
       <c r="E197" s="18" t="n">
@@ -8803,7 +8820,7 @@
       <c r="C198" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D198" s="17" t="n">
+      <c r="D198" s="49" t="n">
         <v>0.46</v>
       </c>
       <c r="E198" s="18" t="n">
@@ -8843,7 +8860,7 @@
       <c r="C199" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D199" s="17" t="n">
+      <c r="D199" s="49" t="n">
         <v>0.65</v>
       </c>
       <c r="E199" s="18" t="n">
@@ -8884,7 +8901,7 @@
         <f>SUM(C166:C199)</f>
         <v/>
       </c>
-      <c r="D200" s="22">
+      <c r="D200" s="50">
         <f>SUM(D166:D199)</f>
         <v/>
       </c>
@@ -8931,7 +8948,7 @@
       <c r="C201" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D201" s="17" t="n">
+      <c r="D201" s="49" t="n">
         <v>242.68</v>
       </c>
       <c r="E201" s="18" t="n">
@@ -8971,7 +8988,7 @@
       <c r="C202" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D202" s="17" t="n">
+      <c r="D202" s="49" t="n">
         <v>243.69</v>
       </c>
       <c r="E202" s="18" t="n">
@@ -9011,7 +9028,7 @@
       <c r="C203" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D203" s="17" t="n">
+      <c r="D203" s="49" t="n">
         <v>243.87</v>
       </c>
       <c r="E203" s="18" t="n">
@@ -9051,7 +9068,7 @@
       <c r="C204" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D204" s="17" t="n">
+      <c r="D204" s="49" t="n">
         <v>199.74</v>
       </c>
       <c r="E204" s="18" t="n">
@@ -9091,7 +9108,7 @@
       <c r="C205" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D205" s="17" t="n">
+      <c r="D205" s="49" t="n">
         <v>199.74</v>
       </c>
       <c r="E205" s="18" t="n">
@@ -9131,7 +9148,7 @@
       <c r="C206" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D206" s="17" t="n">
+      <c r="D206" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E206" s="18" t="n">
@@ -9171,7 +9188,7 @@
       <c r="C207" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D207" s="17" t="n">
+      <c r="D207" s="49" t="n">
         <v>232.2</v>
       </c>
       <c r="E207" s="18" t="n">
@@ -9211,7 +9228,7 @@
       <c r="C208" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D208" s="17" t="n">
+      <c r="D208" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E208" s="18" t="n">
@@ -9251,7 +9268,7 @@
       <c r="C209" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D209" s="17" t="n">
+      <c r="D209" s="49" t="n">
         <v>232.23</v>
       </c>
       <c r="E209" s="18" t="n">
@@ -9291,7 +9308,7 @@
       <c r="C210" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D210" s="17" t="n">
+      <c r="D210" s="49" t="n">
         <v>231.66</v>
       </c>
       <c r="E210" s="18" t="n">
@@ -9331,7 +9348,7 @@
       <c r="C211" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D211" s="17" t="n">
+      <c r="D211" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E211" s="18" t="n">
@@ -9371,7 +9388,7 @@
       <c r="C212" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D212" s="17" t="n">
+      <c r="D212" s="49" t="n">
         <v>199.49</v>
       </c>
       <c r="E212" s="18" t="n">
@@ -9411,7 +9428,7 @@
       <c r="C213" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D213" s="17" t="n">
+      <c r="D213" s="49" t="n">
         <v>94.23</v>
       </c>
       <c r="E213" s="18" t="n">
@@ -9451,7 +9468,7 @@
       <c r="C214" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D214" s="17" t="n">
+      <c r="D214" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E214" s="18" t="n">
@@ -9491,7 +9508,7 @@
       <c r="C215" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D215" s="17" t="n">
+      <c r="D215" s="49" t="n">
         <v>211.3</v>
       </c>
       <c r="E215" s="18" t="n">
@@ -9531,7 +9548,7 @@
       <c r="C216" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D216" s="17" t="n">
+      <c r="D216" s="49" t="n">
         <v>186.69</v>
       </c>
       <c r="E216" s="18" t="n">
@@ -9571,7 +9588,7 @@
       <c r="C217" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D217" s="17" t="n">
+      <c r="D217" s="49" t="n">
         <v>82.51000000000001</v>
       </c>
       <c r="E217" s="18" t="n">
@@ -9611,7 +9628,7 @@
       <c r="C218" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D218" s="17" t="n">
+      <c r="D218" s="49" t="n">
         <v>198.79</v>
       </c>
       <c r="E218" s="18" t="n">
@@ -9651,7 +9668,7 @@
       <c r="C219" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D219" s="17" t="n">
+      <c r="D219" s="49" t="n">
         <v>180.64</v>
       </c>
       <c r="E219" s="18" t="n">
@@ -9691,7 +9708,7 @@
       <c r="C220" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D220" s="17" t="n">
+      <c r="D220" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E220" s="18" t="n">
@@ -9731,7 +9748,7 @@
       <c r="C221" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D221" s="17" t="n">
+      <c r="D221" s="49" t="n">
         <v>169.38</v>
       </c>
       <c r="E221" s="18" t="n">
@@ -9771,7 +9788,7 @@
       <c r="C222" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D222" s="17" t="n">
+      <c r="D222" s="49" t="n">
         <v>187.95</v>
       </c>
       <c r="E222" s="18" t="n">
@@ -9811,7 +9828,7 @@
       <c r="C223" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D223" s="17" t="n">
+      <c r="D223" s="49" t="n">
         <v>198.71</v>
       </c>
       <c r="E223" s="18" t="n">
@@ -9851,7 +9868,7 @@
       <c r="C224" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D224" s="17" t="n">
+      <c r="D224" s="49" t="n">
         <v>231.55</v>
       </c>
       <c r="E224" s="18" t="n">
@@ -9891,7 +9908,7 @@
       <c r="C225" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D225" s="17" t="n">
+      <c r="D225" s="49" t="n">
         <v>197.73</v>
       </c>
       <c r="E225" s="18" t="n">
@@ -9931,7 +9948,7 @@
       <c r="C226" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D226" s="17" t="n">
+      <c r="D226" s="49" t="n">
         <v>81.98999999999999</v>
       </c>
       <c r="E226" s="18" t="n">
@@ -9971,7 +9988,7 @@
       <c r="C227" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D227" s="17" t="n">
+      <c r="D227" s="49" t="n">
         <v>82.51000000000001</v>
       </c>
       <c r="E227" s="18" t="n">
@@ -10011,7 +10028,7 @@
       <c r="C228" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D228" s="17" t="n">
+      <c r="D228" s="49" t="n">
         <v>94.29000000000001</v>
       </c>
       <c r="E228" s="18" t="n">
@@ -10051,7 +10068,7 @@
       <c r="C229" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D229" s="17" t="n">
+      <c r="D229" s="49" t="n">
         <v>91.65000000000001</v>
       </c>
       <c r="E229" s="18" t="n">
@@ -10091,7 +10108,7 @@
       <c r="C230" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D230" s="17" t="n">
+      <c r="D230" s="49" t="n">
         <v>94.17</v>
       </c>
       <c r="E230" s="18" t="n">
@@ -10131,7 +10148,7 @@
       <c r="C231" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D231" s="17" t="n">
+      <c r="D231" s="49" t="n">
         <v>81.39</v>
       </c>
       <c r="E231" s="18" t="n">
@@ -10171,7 +10188,7 @@
       <c r="C232" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D232" s="17" t="n">
+      <c r="D232" s="49" t="n">
         <v>77.77</v>
       </c>
       <c r="E232" s="18" t="n">
@@ -10211,7 +10228,7 @@
       <c r="C233" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D233" s="17" t="n">
+      <c r="D233" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E233" s="18" t="n">
@@ -10251,7 +10268,7 @@
       <c r="C234" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D234" s="17" t="n">
+      <c r="D234" s="49" t="n">
         <v>44.77</v>
       </c>
       <c r="E234" s="18" t="n">
@@ -10291,7 +10308,7 @@
       <c r="C235" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D235" s="17" t="n">
+      <c r="D235" s="49" t="n">
         <v>81.06</v>
       </c>
       <c r="E235" s="18" t="n">
@@ -10331,7 +10348,7 @@
       <c r="C236" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D236" s="17" t="n">
+      <c r="D236" s="49" t="n">
         <v>6</v>
       </c>
       <c r="E236" s="18" t="n">
@@ -10371,7 +10388,7 @@
       <c r="C237" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D237" s="17" t="n">
+      <c r="D237" s="49" t="n">
         <v>0.53</v>
       </c>
       <c r="E237" s="18" t="n">
@@ -10411,7 +10428,7 @@
       <c r="C238" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D238" s="17" t="n">
+      <c r="D238" s="49" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E238" s="18" t="n">
@@ -10451,7 +10468,7 @@
       <c r="C239" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D239" s="17" t="n">
+      <c r="D239" s="49" t="n">
         <v>2.71</v>
       </c>
       <c r="E239" s="18" t="n">
@@ -10492,7 +10509,7 @@
         <f>SUM(C201:C239)</f>
         <v/>
       </c>
-      <c r="D240" s="22">
+      <c r="D240" s="50">
         <f>SUM(D201:D239)</f>
         <v/>
       </c>
@@ -10539,7 +10556,7 @@
       <c r="C241" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D241" s="17" t="n">
+      <c r="D241" s="49" t="n">
         <v>244.01</v>
       </c>
       <c r="E241" s="18" t="n">
@@ -10579,7 +10596,7 @@
       <c r="C242" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D242" s="17" t="n">
+      <c r="D242" s="49" t="n">
         <v>243.67</v>
       </c>
       <c r="E242" s="18" t="n">
@@ -10619,7 +10636,7 @@
       <c r="C243" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D243" s="17" t="n">
+      <c r="D243" s="49" t="n">
         <v>231.68</v>
       </c>
       <c r="E243" s="18" t="n">
@@ -10659,7 +10676,7 @@
       <c r="C244" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D244" s="17" t="n">
+      <c r="D244" s="49" t="n">
         <v>204.06</v>
       </c>
       <c r="E244" s="18" t="n">
@@ -10699,7 +10716,7 @@
       <c r="C245" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D245" s="17" t="n">
+      <c r="D245" s="49" t="n">
         <v>232.24</v>
       </c>
       <c r="E245" s="18" t="n">
@@ -10739,7 +10756,7 @@
       <c r="C246" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D246" s="17" t="n">
+      <c r="D246" s="49" t="n">
         <v>199.74</v>
       </c>
       <c r="E246" s="18" t="n">
@@ -10779,7 +10796,7 @@
       <c r="C247" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D247" s="17" t="n">
+      <c r="D247" s="49" t="n">
         <v>232.23</v>
       </c>
       <c r="E247" s="18" t="n">
@@ -10819,7 +10836,7 @@
       <c r="C248" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D248" s="17" t="n">
+      <c r="D248" s="49" t="n">
         <v>218.97</v>
       </c>
       <c r="E248" s="18" t="n">
@@ -10859,7 +10876,7 @@
       <c r="C249" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D249" s="17" t="n">
+      <c r="D249" s="49" t="n">
         <v>94.27</v>
       </c>
       <c r="E249" s="18" t="n">
@@ -10899,7 +10916,7 @@
       <c r="C250" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D250" s="17" t="n">
+      <c r="D250" s="49" t="n">
         <v>199.04</v>
       </c>
       <c r="E250" s="18" t="n">
@@ -10939,7 +10956,7 @@
       <c r="C251" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D251" s="17" t="n">
+      <c r="D251" s="49" t="n">
         <v>199.48</v>
       </c>
       <c r="E251" s="18" t="n">
@@ -10979,7 +10996,7 @@
       <c r="C252" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D252" s="17" t="n">
+      <c r="D252" s="49" t="n">
         <v>199.19</v>
       </c>
       <c r="E252" s="18" t="n">
@@ -11019,7 +11036,7 @@
       <c r="C253" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D253" s="17" t="n">
+      <c r="D253" s="49" t="n">
         <v>199.04</v>
       </c>
       <c r="E253" s="18" t="n">
@@ -11059,7 +11076,7 @@
       <c r="C254" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D254" s="17" t="n">
+      <c r="D254" s="49" t="n">
         <v>93.77</v>
       </c>
       <c r="E254" s="18" t="n">
@@ -11099,7 +11116,7 @@
       <c r="C255" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D255" s="17" t="n">
+      <c r="D255" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E255" s="18" t="n">
@@ -11139,7 +11156,7 @@
       <c r="C256" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D256" s="17" t="n">
+      <c r="D256" s="49" t="n">
         <v>209.83</v>
       </c>
       <c r="E256" s="18" t="n">
@@ -11179,7 +11196,7 @@
       <c r="C257" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D257" s="17" t="n">
+      <c r="D257" s="49" t="n">
         <v>197.8</v>
       </c>
       <c r="E257" s="18" t="n">
@@ -11219,7 +11236,7 @@
       <c r="C258" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D258" s="17" t="n">
+      <c r="D258" s="49" t="n">
         <v>197</v>
       </c>
       <c r="E258" s="18" t="n">
@@ -11259,7 +11276,7 @@
       <c r="C259" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D259" s="17" t="n">
+      <c r="D259" s="49" t="n">
         <v>186.67</v>
       </c>
       <c r="E259" s="18" t="n">
@@ -11299,7 +11316,7 @@
       <c r="C260" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D260" s="17" t="n">
+      <c r="D260" s="49" t="n">
         <v>82.47</v>
       </c>
       <c r="E260" s="18" t="n">
@@ -11339,7 +11356,7 @@
       <c r="C261" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D261" s="17" t="n">
+      <c r="D261" s="49" t="n">
         <v>93.92</v>
       </c>
       <c r="E261" s="18" t="n">
@@ -11379,7 +11396,7 @@
       <c r="C262" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D262" s="17" t="n">
+      <c r="D262" s="49" t="n">
         <v>81.42</v>
       </c>
       <c r="E262" s="18" t="n">
@@ -11419,7 +11436,7 @@
       <c r="C263" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D263" s="17" t="n">
+      <c r="D263" s="49" t="n">
         <v>232.16</v>
       </c>
       <c r="E263" s="18" t="n">
@@ -11459,7 +11476,7 @@
       <c r="C264" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D264" s="17" t="n">
+      <c r="D264" s="49" t="n">
         <v>82.47</v>
       </c>
       <c r="E264" s="18" t="n">
@@ -11499,7 +11516,7 @@
       <c r="C265" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D265" s="17" t="n">
+      <c r="D265" s="49" t="n">
         <v>81.98999999999999</v>
       </c>
       <c r="E265" s="18" t="n">
@@ -11539,7 +11556,7 @@
       <c r="C266" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D266" s="17" t="n">
+      <c r="D266" s="49" t="n">
         <v>79.42</v>
       </c>
       <c r="E266" s="18" t="n">
@@ -11579,7 +11596,7 @@
       <c r="C267" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D267" s="17" t="n">
+      <c r="D267" s="49" t="n">
         <v>82.64</v>
       </c>
       <c r="E267" s="18" t="n">
@@ -11619,7 +11636,7 @@
       <c r="C268" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D268" s="17" t="n">
+      <c r="D268" s="49" t="n">
         <v>94.03</v>
       </c>
       <c r="E268" s="18" t="n">
@@ -11659,7 +11676,7 @@
       <c r="C269" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D269" s="17" t="n">
+      <c r="D269" s="49" t="n">
         <v>81.65000000000001</v>
       </c>
       <c r="E269" s="18" t="n">
@@ -11699,7 +11716,7 @@
       <c r="C270" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D270" s="17" t="n">
+      <c r="D270" s="49" t="n">
         <v>59.48</v>
       </c>
       <c r="E270" s="18" t="n">
@@ -11739,7 +11756,7 @@
       <c r="C271" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D271" s="17" t="n">
+      <c r="D271" s="49" t="n">
         <v>11.38</v>
       </c>
       <c r="E271" s="18" t="n">
@@ -11779,7 +11796,7 @@
       <c r="C272" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D272" s="17" t="n">
+      <c r="D272" s="49" t="n">
         <v>0.52</v>
       </c>
       <c r="E272" s="18" t="n">
@@ -11819,7 +11836,7 @@
       <c r="C273" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D273" s="17" t="n">
+      <c r="D273" s="49" t="n">
         <v>0.49</v>
       </c>
       <c r="E273" s="18" t="n">
@@ -11859,7 +11876,7 @@
       <c r="C274" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D274" s="17" t="n">
+      <c r="D274" s="49" t="n">
         <v>0.05</v>
       </c>
       <c r="E274" s="18" t="n">
@@ -11900,7 +11917,7 @@
         <f>SUM(C241:C274)</f>
         <v/>
       </c>
-      <c r="D275" s="22">
+      <c r="D275" s="50">
         <f>SUM(D241:D274)</f>
         <v/>
       </c>
@@ -11944,7 +11961,7 @@
         <f>C41+C81+C123+C165+C200+C240+C275</f>
         <v/>
       </c>
-      <c r="D276" s="27">
+      <c r="D276" s="51">
         <f>D41+D81+D123+D165+D200+D240+D275</f>
         <v/>
       </c>
@@ -12024,7 +12041,7 @@
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
-          <t>Total EB = 114   ·   Valid trips = 6   ·   Non-valid trips = 108   ·   Undesirable = 50</t>
+          <t>Total EB = 114   ·   Valid trips = 6   ·   Non-valid trips = 108   ·   Undesirable = 54</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12441,7 @@
       </c>
       <c r="P9" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>StandBy Mode</t>
         </is>
       </c>
       <c r="Q9" s="31" t="inlineStr">
@@ -13846,7 +13863,7 @@
       </c>
       <c r="P27" s="34" t="inlineStr">
         <is>
-          <t>EB at 0-1 km/h (Standby)</t>
+          <t>EB at 0-1 km/h; StandBy Mode</t>
         </is>
       </c>
       <c r="Q27" s="31" t="inlineStr">
@@ -14399,7 +14416,7 @@
       </c>
       <c r="P34" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>StandBy Mode</t>
         </is>
       </c>
       <c r="Q34" s="31" t="inlineStr">
@@ -18827,7 +18844,7 @@
       </c>
       <c r="P90" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>StandBy Mode</t>
         </is>
       </c>
       <c r="Q90" s="31" t="inlineStr">
@@ -20645,7 +20662,7 @@
       </c>
       <c r="P113" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>StandBy Mode</t>
         </is>
       </c>
       <c r="Q113" s="31" t="inlineStr">
@@ -76149,7 +76166,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -93173,7 +93189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -93188,7 +93204,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>

--- a/docs/reports/ER_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/ER_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -732,7 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -957,6 +956,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2518,7 +2524,7 @@
         <v/>
       </c>
       <c r="F41" s="23">
-        <f>SUM(F4:F40)</f>
+        <f>SUMIF(E4:E40,"&gt;0",F4:F40)</f>
         <v/>
       </c>
       <c r="G41" s="24">
@@ -4126,7 +4132,7 @@
         <v/>
       </c>
       <c r="F81" s="23">
-        <f>SUM(F42:F80)</f>
+        <f>SUMIF(E42:E80,"&gt;0",F42:F80)</f>
         <v/>
       </c>
       <c r="G81" s="24">
@@ -5814,7 +5820,7 @@
         <v/>
       </c>
       <c r="F123" s="23">
-        <f>SUM(F82:F122)</f>
+        <f>SUMIF(E82:E122,"&gt;0",F82:F122)</f>
         <v/>
       </c>
       <c r="G123" s="24">
@@ -7502,7 +7508,7 @@
         <v/>
       </c>
       <c r="F165" s="23">
-        <f>SUM(F124:F164)</f>
+        <f>SUMIF(E124:E164,"&gt;0",F124:F164)</f>
         <v/>
       </c>
       <c r="G165" s="24">
@@ -8910,7 +8916,7 @@
         <v/>
       </c>
       <c r="F200" s="23">
-        <f>SUM(F166:F199)</f>
+        <f>SUMIF(E166:E199,"&gt;0",F166:F199)</f>
         <v/>
       </c>
       <c r="G200" s="24">
@@ -10518,7 +10524,7 @@
         <v/>
       </c>
       <c r="F240" s="23">
-        <f>SUM(F201:F239)</f>
+        <f>SUMIF(E201:E239,"&gt;0",F201:F239)</f>
         <v/>
       </c>
       <c r="G240" s="24">
@@ -11926,7 +11932,7 @@
         <v/>
       </c>
       <c r="F275" s="23">
-        <f>SUM(F241:F274)</f>
+        <f>SUMIF(E241:E274,"&gt;0",F241:F274)</f>
         <v/>
       </c>
       <c r="G275" s="24">
@@ -12037,7 +12043,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -12045,7 +12050,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
